--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356675</v>
       </c>
       <c r="B2" t="n">
-        <v>90047</v>
+        <v>90063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113356688</v>
       </c>
       <c r="B3" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356675</v>
+        <v>113356688</v>
       </c>
       <c r="B2" t="n">
-        <v>90063</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750790</v>
+        <v>750762</v>
       </c>
       <c r="R2" t="n">
-        <v>7192998</v>
+        <v>7192958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356688</v>
+        <v>113356675</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>90075</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750762</v>
+        <v>750790</v>
       </c>
       <c r="R3" t="n">
-        <v>7192958</v>
+        <v>7192998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356688</v>
+        <v>113356675</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>90075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750762</v>
+        <v>750790</v>
       </c>
       <c r="R2" t="n">
-        <v>7192958</v>
+        <v>7192998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356675</v>
+        <v>113356688</v>
       </c>
       <c r="B3" t="n">
-        <v>90075</v>
+        <v>78133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750790</v>
+        <v>750762</v>
       </c>
       <c r="R3" t="n">
-        <v>7192998</v>
+        <v>7192958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356675</v>
       </c>
       <c r="B2" t="n">
-        <v>90075</v>
+        <v>90097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113356688</v>
       </c>
       <c r="B3" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356675</v>
       </c>
       <c r="B2" t="n">
-        <v>90097</v>
+        <v>90101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113356688</v>
       </c>
       <c r="B3" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356675</v>
+        <v>113356688</v>
       </c>
       <c r="B2" t="n">
-        <v>90101</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750790</v>
+        <v>750762</v>
       </c>
       <c r="R2" t="n">
-        <v>7192998</v>
+        <v>7192958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356688</v>
+        <v>113356675</v>
       </c>
       <c r="B3" t="n">
-        <v>78158</v>
+        <v>90101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750762</v>
+        <v>750790</v>
       </c>
       <c r="R3" t="n">
-        <v>7192958</v>
+        <v>7192998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356688</v>
+        <v>113356675</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>90107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750762</v>
+        <v>750790</v>
       </c>
       <c r="R2" t="n">
-        <v>7192958</v>
+        <v>7192998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356675</v>
+        <v>113356688</v>
       </c>
       <c r="B3" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750790</v>
+        <v>750762</v>
       </c>
       <c r="R3" t="n">
-        <v>7192998</v>
+        <v>7192958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356675</v>
       </c>
       <c r="B2" t="n">
-        <v>90107</v>
+        <v>90114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113356688</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356675</v>
+        <v>113356688</v>
       </c>
       <c r="B2" t="n">
-        <v>90114</v>
+        <v>78173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750790</v>
+        <v>750762</v>
       </c>
       <c r="R2" t="n">
-        <v>7192998</v>
+        <v>7192958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356688</v>
+        <v>113356675</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>90117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750762</v>
+        <v>750790</v>
       </c>
       <c r="R3" t="n">
-        <v>7192958</v>
+        <v>7192998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356688</v>
+        <v>113356675</v>
       </c>
       <c r="B2" t="n">
-        <v>78173</v>
+        <v>90148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750762</v>
+        <v>750790</v>
       </c>
       <c r="R2" t="n">
-        <v>7192958</v>
+        <v>7192998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356675</v>
+        <v>113356688</v>
       </c>
       <c r="B3" t="n">
-        <v>90117</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750790</v>
+        <v>750762</v>
       </c>
       <c r="R3" t="n">
-        <v>7192998</v>
+        <v>7192958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,6 +884,3216 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113703192</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79265</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>750737</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7192696</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113703202</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>750725</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7192721</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113703204</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97418</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>750792</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7192947</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113703211</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>750676</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7192911</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113703212</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90149</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>750715</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7193010</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113703193</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78236</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>750514</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7192817</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113703223</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90149</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>750773</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7193000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113703194</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>750520</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7192806</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113703218</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>750692</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7192995</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113703196</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90095</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>750481</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7192771</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113703222</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90149</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>750782</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7192990</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113703220</v>
+      </c>
+      <c r="B15" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>750786</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7192980</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113703195</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97418</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>750470</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7192856</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113703216</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90131</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>750665</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7193040</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113703221</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90149</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>750789</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7193000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113703168</v>
+      </c>
+      <c r="B19" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>750652</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7192891</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113703199</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79299</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>750567</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7192769</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113703200</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79265</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>750567</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7192769</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113703169</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>750724</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7193030</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113703198</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90131</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>750498</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7192778</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113703215</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90149</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>750649</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7193005</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>113703190</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79299</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>750736</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7192698</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113703188</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>750810</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7192675</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113703217</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90131</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>750701</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7193021</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113703201</v>
+      </c>
+      <c r="B28" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>750591</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7192765</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113703197</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79199</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>750492</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7192773</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113703213</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90095</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>750660</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7193051</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113703191</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79298</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>750735</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7192695</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>113703210</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90149</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>750636</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7192848</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>113703219</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90131</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>750793</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7192970</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356675</v>
+        <v>113356688</v>
       </c>
       <c r="B2" t="n">
-        <v>90148</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750790</v>
+        <v>750762</v>
       </c>
       <c r="R2" t="n">
-        <v>7192998</v>
+        <v>7192958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356688</v>
+        <v>113356675</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>90149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750762</v>
+        <v>750790</v>
       </c>
       <c r="R3" t="n">
-        <v>7192958</v>
+        <v>7192998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703192</v>
+        <v>113703212</v>
       </c>
       <c r="B4" t="n">
-        <v>79265</v>
+        <v>90149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750737</v>
+        <v>750715</v>
       </c>
       <c r="R4" t="n">
-        <v>7192696</v>
+        <v>7193010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703202</v>
+        <v>113703213</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>90095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750725</v>
+        <v>750660</v>
       </c>
       <c r="R5" t="n">
-        <v>7192721</v>
+        <v>7193051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703204</v>
+        <v>113703221</v>
       </c>
       <c r="B6" t="n">
-        <v>97418</v>
+        <v>90149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750792</v>
+        <v>750789</v>
       </c>
       <c r="R6" t="n">
-        <v>7192947</v>
+        <v>7193000</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703211</v>
+        <v>113703169</v>
       </c>
       <c r="B7" t="n">
         <v>78201</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750676</v>
+        <v>750724</v>
       </c>
       <c r="R7" t="n">
-        <v>7192911</v>
+        <v>7193030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113703212</v>
+        <v>113703216</v>
       </c>
       <c r="B8" t="n">
-        <v>90149</v>
+        <v>90131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750715</v>
+        <v>750665</v>
       </c>
       <c r="R8" t="n">
-        <v>7193010</v>
+        <v>7193040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113703193</v>
+        <v>113703200</v>
       </c>
       <c r="B9" t="n">
-        <v>78236</v>
+        <v>79265</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750514</v>
+        <v>750567</v>
       </c>
       <c r="R9" t="n">
-        <v>7192817</v>
+        <v>7192769</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113703223</v>
+        <v>113703195</v>
       </c>
       <c r="B10" t="n">
-        <v>90149</v>
+        <v>97418</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750773</v>
+        <v>750470</v>
       </c>
       <c r="R10" t="n">
-        <v>7193000</v>
+        <v>7192856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113703194</v>
+        <v>113703220</v>
       </c>
       <c r="B11" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750520</v>
+        <v>750786</v>
       </c>
       <c r="R11" t="n">
-        <v>7192806</v>
+        <v>7192980</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113703218</v>
+        <v>113703210</v>
       </c>
       <c r="B12" t="n">
-        <v>78201</v>
+        <v>90149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750692</v>
+        <v>750636</v>
       </c>
       <c r="R12" t="n">
-        <v>7192995</v>
+        <v>7192848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113703196</v>
+        <v>113703218</v>
       </c>
       <c r="B13" t="n">
-        <v>90095</v>
+        <v>78201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750481</v>
+        <v>750692</v>
       </c>
       <c r="R13" t="n">
-        <v>7192771</v>
+        <v>7192995</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113703222</v>
+        <v>113703168</v>
       </c>
       <c r="B14" t="n">
-        <v>90149</v>
+        <v>81944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750782</v>
+        <v>750652</v>
       </c>
       <c r="R14" t="n">
-        <v>7192990</v>
+        <v>7192891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113703220</v>
+        <v>113703215</v>
       </c>
       <c r="B15" t="n">
-        <v>81944</v>
+        <v>90149</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750786</v>
+        <v>750649</v>
       </c>
       <c r="R15" t="n">
-        <v>7192980</v>
+        <v>7193005</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113703195</v>
+        <v>113703193</v>
       </c>
       <c r="B16" t="n">
-        <v>97418</v>
+        <v>78236</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,25 +2183,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750470</v>
+        <v>750514</v>
       </c>
       <c r="R16" t="n">
-        <v>7192856</v>
+        <v>7192817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113703216</v>
+        <v>113703202</v>
       </c>
       <c r="B17" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750665</v>
+        <v>750725</v>
       </c>
       <c r="R17" t="n">
-        <v>7193040</v>
+        <v>7192721</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113703221</v>
+        <v>113703211</v>
       </c>
       <c r="B18" t="n">
-        <v>90149</v>
+        <v>78201</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,21 +2401,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750789</v>
+        <v>750676</v>
       </c>
       <c r="R18" t="n">
-        <v>7193000</v>
+        <v>7192911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113703168</v>
+        <v>113703204</v>
       </c>
       <c r="B19" t="n">
-        <v>81944</v>
+        <v>97418</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2504,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750652</v>
+        <v>750792</v>
       </c>
       <c r="R19" t="n">
-        <v>7192891</v>
+        <v>7192947</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113703200</v>
+        <v>113703188</v>
       </c>
       <c r="B21" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750567</v>
+        <v>750810</v>
       </c>
       <c r="R21" t="n">
-        <v>7192769</v>
+        <v>7192675</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113703169</v>
+        <v>113703197</v>
       </c>
       <c r="B22" t="n">
-        <v>78201</v>
+        <v>79199</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,25 +2825,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750724</v>
+        <v>750492</v>
       </c>
       <c r="R22" t="n">
-        <v>7193030</v>
+        <v>7192773</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113703198</v>
+        <v>113703192</v>
       </c>
       <c r="B23" t="n">
-        <v>90131</v>
+        <v>79265</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750498</v>
+        <v>750737</v>
       </c>
       <c r="R23" t="n">
-        <v>7192778</v>
+        <v>7192696</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113703215</v>
+        <v>113703217</v>
       </c>
       <c r="B24" t="n">
-        <v>90149</v>
+        <v>90131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750649</v>
+        <v>750701</v>
       </c>
       <c r="R24" t="n">
-        <v>7193005</v>
+        <v>7193021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113703188</v>
+        <v>113703222</v>
       </c>
       <c r="B26" t="n">
-        <v>78201</v>
+        <v>90149</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750810</v>
+        <v>750782</v>
       </c>
       <c r="R26" t="n">
-        <v>7192675</v>
+        <v>7192990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113703217</v>
+        <v>113703196</v>
       </c>
       <c r="B27" t="n">
-        <v>90131</v>
+        <v>90095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,25 +3360,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750701</v>
+        <v>750481</v>
       </c>
       <c r="R27" t="n">
-        <v>7193021</v>
+        <v>7192771</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113703201</v>
+        <v>113703198</v>
       </c>
       <c r="B28" t="n">
-        <v>81944</v>
+        <v>90131</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>750591</v>
+        <v>750498</v>
       </c>
       <c r="R28" t="n">
-        <v>7192765</v>
+        <v>7192778</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113703197</v>
+        <v>113703219</v>
       </c>
       <c r="B29" t="n">
-        <v>79199</v>
+        <v>90131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,25 +3574,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750492</v>
+        <v>750793</v>
       </c>
       <c r="R29" t="n">
-        <v>7192773</v>
+        <v>7192970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113703213</v>
+        <v>113703191</v>
       </c>
       <c r="B30" t="n">
-        <v>90095</v>
+        <v>79298</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750660</v>
+        <v>750735</v>
       </c>
       <c r="R30" t="n">
-        <v>7193051</v>
+        <v>7192695</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113703191</v>
+        <v>113703223</v>
       </c>
       <c r="B31" t="n">
-        <v>79298</v>
+        <v>90149</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,25 +3788,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>750735</v>
+        <v>750773</v>
       </c>
       <c r="R31" t="n">
-        <v>7192695</v>
+        <v>7193000</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113703210</v>
+        <v>113703194</v>
       </c>
       <c r="B32" t="n">
-        <v>90149</v>
+        <v>78201</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3899,21 +3899,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750636</v>
+        <v>750520</v>
       </c>
       <c r="R32" t="n">
-        <v>7192848</v>
+        <v>7192806</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113703219</v>
+        <v>113703201</v>
       </c>
       <c r="B33" t="n">
-        <v>90131</v>
+        <v>81944</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>750793</v>
+        <v>750591</v>
       </c>
       <c r="R33" t="n">
-        <v>7192970</v>
+        <v>7192765</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703212</v>
+        <v>113703220</v>
       </c>
       <c r="B4" t="n">
-        <v>90149</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750715</v>
+        <v>750786</v>
       </c>
       <c r="R4" t="n">
-        <v>7193010</v>
+        <v>7192980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703213</v>
+        <v>113703190</v>
       </c>
       <c r="B5" t="n">
-        <v>90095</v>
+        <v>79299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750660</v>
+        <v>750736</v>
       </c>
       <c r="R5" t="n">
-        <v>7193051</v>
+        <v>7192698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703221</v>
+        <v>113703202</v>
       </c>
       <c r="B6" t="n">
-        <v>90149</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750789</v>
+        <v>750725</v>
       </c>
       <c r="R6" t="n">
-        <v>7193000</v>
+        <v>7192721</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703169</v>
+        <v>113703216</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750724</v>
+        <v>750665</v>
       </c>
       <c r="R7" t="n">
-        <v>7193030</v>
+        <v>7193040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113703216</v>
+        <v>113703223</v>
       </c>
       <c r="B8" t="n">
-        <v>90131</v>
+        <v>90153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750665</v>
+        <v>750773</v>
       </c>
       <c r="R8" t="n">
-        <v>7193040</v>
+        <v>7193000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113703200</v>
+        <v>113703212</v>
       </c>
       <c r="B9" t="n">
-        <v>79265</v>
+        <v>90153</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750567</v>
+        <v>750715</v>
       </c>
       <c r="R9" t="n">
-        <v>7192769</v>
+        <v>7193010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113703195</v>
+        <v>113703193</v>
       </c>
       <c r="B10" t="n">
-        <v>97418</v>
+        <v>78236</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750470</v>
+        <v>750514</v>
       </c>
       <c r="R10" t="n">
-        <v>7192856</v>
+        <v>7192817</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113703220</v>
+        <v>113703194</v>
       </c>
       <c r="B11" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750786</v>
+        <v>750520</v>
       </c>
       <c r="R11" t="n">
-        <v>7192980</v>
+        <v>7192806</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
         <v>113703210</v>
       </c>
       <c r="B12" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113703168</v>
+        <v>113703204</v>
       </c>
       <c r="B14" t="n">
-        <v>81944</v>
+        <v>97422</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750652</v>
+        <v>750792</v>
       </c>
       <c r="R14" t="n">
-        <v>7192891</v>
+        <v>7192947</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113703215</v>
+        <v>113703224</v>
       </c>
       <c r="B15" t="n">
-        <v>90149</v>
+        <v>78201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750649</v>
+        <v>750724</v>
       </c>
       <c r="R15" t="n">
-        <v>7193005</v>
+        <v>7193030</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113703193</v>
+        <v>113703201</v>
       </c>
       <c r="B16" t="n">
-        <v>78236</v>
+        <v>81944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750514</v>
+        <v>750591</v>
       </c>
       <c r="R16" t="n">
-        <v>7192817</v>
+        <v>7192765</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113703202</v>
+        <v>113703217</v>
       </c>
       <c r="B17" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750725</v>
+        <v>750701</v>
       </c>
       <c r="R17" t="n">
-        <v>7192721</v>
+        <v>7193021</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113703211</v>
+        <v>113703197</v>
       </c>
       <c r="B18" t="n">
-        <v>78201</v>
+        <v>79199</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750676</v>
+        <v>750492</v>
       </c>
       <c r="R18" t="n">
-        <v>7192911</v>
+        <v>7192773</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113703204</v>
+        <v>113703191</v>
       </c>
       <c r="B19" t="n">
-        <v>97418</v>
+        <v>79298</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750792</v>
+        <v>750735</v>
       </c>
       <c r="R19" t="n">
-        <v>7192947</v>
+        <v>7192695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113703199</v>
+        <v>113703215</v>
       </c>
       <c r="B20" t="n">
-        <v>79299</v>
+        <v>90153</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,25 +2611,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750567</v>
+        <v>750649</v>
       </c>
       <c r="R20" t="n">
-        <v>7192769</v>
+        <v>7193005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113703188</v>
+        <v>113703199</v>
       </c>
       <c r="B21" t="n">
-        <v>78201</v>
+        <v>79299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,25 +2718,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750810</v>
+        <v>750567</v>
       </c>
       <c r="R21" t="n">
-        <v>7192675</v>
+        <v>7192769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113703197</v>
+        <v>113703168</v>
       </c>
       <c r="B22" t="n">
-        <v>79199</v>
+        <v>81944</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,25 +2825,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750492</v>
+        <v>750652</v>
       </c>
       <c r="R22" t="n">
-        <v>7192773</v>
+        <v>7192891</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113703217</v>
+        <v>113703188</v>
       </c>
       <c r="B24" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750701</v>
+        <v>750810</v>
       </c>
       <c r="R24" t="n">
-        <v>7193021</v>
+        <v>7192675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113703190</v>
+        <v>113703211</v>
       </c>
       <c r="B25" t="n">
-        <v>79299</v>
+        <v>78201</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3146,25 +3146,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750736</v>
+        <v>750676</v>
       </c>
       <c r="R25" t="n">
-        <v>7192698</v>
+        <v>7192911</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113703222</v>
+        <v>113703219</v>
       </c>
       <c r="B26" t="n">
-        <v>90149</v>
+        <v>90135</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750782</v>
+        <v>750793</v>
       </c>
       <c r="R26" t="n">
-        <v>7192990</v>
+        <v>7192970</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113703196</v>
+        <v>113703195</v>
       </c>
       <c r="B27" t="n">
-        <v>90095</v>
+        <v>97422</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3364,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750481</v>
+        <v>750470</v>
       </c>
       <c r="R27" t="n">
-        <v>7192771</v>
+        <v>7192856</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113703198</v>
+        <v>113703196</v>
       </c>
       <c r="B28" t="n">
-        <v>90131</v>
+        <v>90099</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,25 +3467,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>750498</v>
+        <v>750481</v>
       </c>
       <c r="R28" t="n">
-        <v>7192778</v>
+        <v>7192771</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113703219</v>
+        <v>113703200</v>
       </c>
       <c r="B29" t="n">
-        <v>90131</v>
+        <v>79265</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750793</v>
+        <v>750567</v>
       </c>
       <c r="R29" t="n">
-        <v>7192970</v>
+        <v>7192769</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113703191</v>
+        <v>113703222</v>
       </c>
       <c r="B30" t="n">
-        <v>79298</v>
+        <v>90153</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750735</v>
+        <v>750782</v>
       </c>
       <c r="R30" t="n">
-        <v>7192695</v>
+        <v>7192990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113703223</v>
+        <v>113703213</v>
       </c>
       <c r="B31" t="n">
-        <v>90149</v>
+        <v>90099</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,25 +3788,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>750773</v>
+        <v>750660</v>
       </c>
       <c r="R31" t="n">
-        <v>7193000</v>
+        <v>7193051</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113703194</v>
+        <v>113703198</v>
       </c>
       <c r="B32" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3899,21 +3899,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750520</v>
+        <v>750498</v>
       </c>
       <c r="R32" t="n">
-        <v>7192806</v>
+        <v>7192778</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113703201</v>
+        <v>113703221</v>
       </c>
       <c r="B33" t="n">
-        <v>81944</v>
+        <v>90153</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>750591</v>
+        <v>750789</v>
       </c>
       <c r="R33" t="n">
-        <v>7192765</v>
+        <v>7193000</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703220</v>
+        <v>113703195</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>97422</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750786</v>
+        <v>750470</v>
       </c>
       <c r="R4" t="n">
-        <v>7192980</v>
+        <v>7192856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703190</v>
+        <v>113703212</v>
       </c>
       <c r="B5" t="n">
-        <v>79299</v>
+        <v>90153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750736</v>
+        <v>750715</v>
       </c>
       <c r="R5" t="n">
-        <v>7192698</v>
+        <v>7193010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703202</v>
+        <v>113703200</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>79265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750725</v>
+        <v>750567</v>
       </c>
       <c r="R6" t="n">
-        <v>7192721</v>
+        <v>7192769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703216</v>
+        <v>113703215</v>
       </c>
       <c r="B7" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750665</v>
+        <v>750649</v>
       </c>
       <c r="R7" t="n">
-        <v>7193040</v>
+        <v>7193005</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113703223</v>
+        <v>113703188</v>
       </c>
       <c r="B8" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750773</v>
+        <v>750810</v>
       </c>
       <c r="R8" t="n">
-        <v>7193000</v>
+        <v>7192675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113703212</v>
+        <v>113703197</v>
       </c>
       <c r="B9" t="n">
-        <v>90153</v>
+        <v>79199</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750715</v>
+        <v>750492</v>
       </c>
       <c r="R9" t="n">
-        <v>7193010</v>
+        <v>7192773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113703193</v>
+        <v>113703204</v>
       </c>
       <c r="B10" t="n">
-        <v>78236</v>
+        <v>97422</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750514</v>
+        <v>750792</v>
       </c>
       <c r="R10" t="n">
-        <v>7192817</v>
+        <v>7192947</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113703194</v>
+        <v>113703199</v>
       </c>
       <c r="B11" t="n">
-        <v>78201</v>
+        <v>79299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750520</v>
+        <v>750567</v>
       </c>
       <c r="R11" t="n">
-        <v>7192806</v>
+        <v>7192769</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113703210</v>
+        <v>113703196</v>
       </c>
       <c r="B12" t="n">
-        <v>90153</v>
+        <v>90099</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750636</v>
+        <v>750481</v>
       </c>
       <c r="R12" t="n">
-        <v>7192848</v>
+        <v>7192771</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113703218</v>
+        <v>113703193</v>
       </c>
       <c r="B13" t="n">
-        <v>78201</v>
+        <v>78236</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750692</v>
+        <v>750514</v>
       </c>
       <c r="R13" t="n">
-        <v>7192995</v>
+        <v>7192817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113703204</v>
+        <v>113703220</v>
       </c>
       <c r="B14" t="n">
-        <v>97422</v>
+        <v>81944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750792</v>
+        <v>750786</v>
       </c>
       <c r="R14" t="n">
-        <v>7192947</v>
+        <v>7192980</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113703224</v>
+        <v>113703218</v>
       </c>
       <c r="B15" t="n">
         <v>78201</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750724</v>
+        <v>750692</v>
       </c>
       <c r="R15" t="n">
-        <v>7193030</v>
+        <v>7192995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113703201</v>
+        <v>113703191</v>
       </c>
       <c r="B16" t="n">
-        <v>81944</v>
+        <v>79298</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,25 +2183,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750591</v>
+        <v>750735</v>
       </c>
       <c r="R16" t="n">
-        <v>7192765</v>
+        <v>7192695</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113703217</v>
+        <v>113703213</v>
       </c>
       <c r="B17" t="n">
-        <v>90135</v>
+        <v>90099</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,25 +2290,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750701</v>
+        <v>750660</v>
       </c>
       <c r="R17" t="n">
-        <v>7193021</v>
+        <v>7193051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113703197</v>
+        <v>113703192</v>
       </c>
       <c r="B18" t="n">
-        <v>79199</v>
+        <v>79265</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750492</v>
+        <v>750737</v>
       </c>
       <c r="R18" t="n">
-        <v>7192773</v>
+        <v>7192696</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113703191</v>
+        <v>113703224</v>
       </c>
       <c r="B19" t="n">
-        <v>79298</v>
+        <v>78201</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,20 +2504,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750735</v>
+        <v>750724</v>
       </c>
       <c r="R19" t="n">
-        <v>7192695</v>
+        <v>7193030</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113703215</v>
+        <v>113703221</v>
       </c>
       <c r="B20" t="n">
         <v>90153</v>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750649</v>
+        <v>750789</v>
       </c>
       <c r="R20" t="n">
-        <v>7193005</v>
+        <v>7193000</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113703199</v>
+        <v>113703223</v>
       </c>
       <c r="B21" t="n">
-        <v>79299</v>
+        <v>90153</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,25 +2718,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750567</v>
+        <v>750773</v>
       </c>
       <c r="R21" t="n">
-        <v>7192769</v>
+        <v>7193000</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113703168</v>
+        <v>113703219</v>
       </c>
       <c r="B22" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750652</v>
+        <v>750793</v>
       </c>
       <c r="R22" t="n">
-        <v>7192891</v>
+        <v>7192970</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113703192</v>
+        <v>113703211</v>
       </c>
       <c r="B23" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750737</v>
+        <v>750676</v>
       </c>
       <c r="R23" t="n">
-        <v>7192696</v>
+        <v>7192911</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3027,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113703188</v>
+        <v>113703202</v>
       </c>
       <c r="B24" t="n">
         <v>78201</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750810</v>
+        <v>750725</v>
       </c>
       <c r="R24" t="n">
-        <v>7192675</v>
+        <v>7192721</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113703211</v>
+        <v>113703217</v>
       </c>
       <c r="B25" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750676</v>
+        <v>750701</v>
       </c>
       <c r="R25" t="n">
-        <v>7192911</v>
+        <v>7193021</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113703219</v>
+        <v>113703168</v>
       </c>
       <c r="B26" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750793</v>
+        <v>750652</v>
       </c>
       <c r="R26" t="n">
-        <v>7192970</v>
+        <v>7192891</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113703195</v>
+        <v>113703198</v>
       </c>
       <c r="B27" t="n">
-        <v>97422</v>
+        <v>90135</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,25 +3360,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750470</v>
+        <v>750498</v>
       </c>
       <c r="R27" t="n">
-        <v>7192856</v>
+        <v>7192778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113703196</v>
+        <v>113703210</v>
       </c>
       <c r="B28" t="n">
-        <v>90099</v>
+        <v>90153</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,25 +3467,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>750481</v>
+        <v>750636</v>
       </c>
       <c r="R28" t="n">
-        <v>7192771</v>
+        <v>7192848</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113703200</v>
+        <v>113703222</v>
       </c>
       <c r="B29" t="n">
-        <v>79265</v>
+        <v>90153</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750567</v>
+        <v>750782</v>
       </c>
       <c r="R29" t="n">
-        <v>7192769</v>
+        <v>7192990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113703222</v>
+        <v>113703194</v>
       </c>
       <c r="B30" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750782</v>
+        <v>750520</v>
       </c>
       <c r="R30" t="n">
-        <v>7192990</v>
+        <v>7192806</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113703213</v>
+        <v>113703190</v>
       </c>
       <c r="B31" t="n">
-        <v>90099</v>
+        <v>79299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3792,21 +3792,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>750660</v>
+        <v>750736</v>
       </c>
       <c r="R31" t="n">
-        <v>7193051</v>
+        <v>7192698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113703198</v>
+        <v>113703201</v>
       </c>
       <c r="B32" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3899,21 +3899,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750498</v>
+        <v>750591</v>
       </c>
       <c r="R32" t="n">
-        <v>7192778</v>
+        <v>7192765</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113703221</v>
+        <v>113703216</v>
       </c>
       <c r="B33" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>750789</v>
+        <v>750665</v>
       </c>
       <c r="R33" t="n">
-        <v>7193000</v>
+        <v>7193040</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703212</v>
+        <v>113703197</v>
       </c>
       <c r="B5" t="n">
-        <v>90153</v>
+        <v>79199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750715</v>
+        <v>750492</v>
       </c>
       <c r="R5" t="n">
-        <v>7193010</v>
+        <v>7192773</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703200</v>
+        <v>113703216</v>
       </c>
       <c r="B6" t="n">
-        <v>79265</v>
+        <v>90135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750567</v>
+        <v>750665</v>
       </c>
       <c r="R6" t="n">
-        <v>7192769</v>
+        <v>7193040</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703215</v>
+        <v>113703194</v>
       </c>
       <c r="B7" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750649</v>
+        <v>750520</v>
       </c>
       <c r="R7" t="n">
-        <v>7193005</v>
+        <v>7192806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113703188</v>
+        <v>113703202</v>
       </c>
       <c r="B8" t="n">
         <v>78201</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750810</v>
+        <v>750725</v>
       </c>
       <c r="R8" t="n">
-        <v>7192675</v>
+        <v>7192721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113703197</v>
+        <v>113703212</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>90153</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750492</v>
+        <v>750715</v>
       </c>
       <c r="R9" t="n">
-        <v>7192773</v>
+        <v>7193010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113703204</v>
+        <v>113703215</v>
       </c>
       <c r="B10" t="n">
-        <v>97422</v>
+        <v>90153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750792</v>
+        <v>750649</v>
       </c>
       <c r="R10" t="n">
-        <v>7192947</v>
+        <v>7193005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113703199</v>
+        <v>113703196</v>
       </c>
       <c r="B11" t="n">
-        <v>79299</v>
+        <v>90099</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750567</v>
+        <v>750481</v>
       </c>
       <c r="R11" t="n">
-        <v>7192769</v>
+        <v>7192771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113703196</v>
+        <v>113703204</v>
       </c>
       <c r="B12" t="n">
-        <v>90099</v>
+        <v>97422</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750481</v>
+        <v>750792</v>
       </c>
       <c r="R12" t="n">
-        <v>7192771</v>
+        <v>7192947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113703193</v>
+        <v>113703221</v>
       </c>
       <c r="B13" t="n">
-        <v>78236</v>
+        <v>90153</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750514</v>
+        <v>750789</v>
       </c>
       <c r="R13" t="n">
-        <v>7192817</v>
+        <v>7193000</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113703220</v>
+        <v>113703210</v>
       </c>
       <c r="B14" t="n">
-        <v>81944</v>
+        <v>90153</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750786</v>
+        <v>750636</v>
       </c>
       <c r="R14" t="n">
-        <v>7192980</v>
+        <v>7192848</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113703218</v>
+        <v>113703217</v>
       </c>
       <c r="B15" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750692</v>
+        <v>750701</v>
       </c>
       <c r="R15" t="n">
-        <v>7192995</v>
+        <v>7193021</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113703191</v>
+        <v>113703218</v>
       </c>
       <c r="B16" t="n">
-        <v>79298</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,20 +2183,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750735</v>
+        <v>750692</v>
       </c>
       <c r="R16" t="n">
-        <v>7192695</v>
+        <v>7192995</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113703213</v>
+        <v>113703222</v>
       </c>
       <c r="B17" t="n">
-        <v>90099</v>
+        <v>90153</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,25 +2290,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750660</v>
+        <v>750782</v>
       </c>
       <c r="R17" t="n">
-        <v>7193051</v>
+        <v>7192990</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113703192</v>
+        <v>113703190</v>
       </c>
       <c r="B18" t="n">
-        <v>79265</v>
+        <v>79299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750737</v>
+        <v>750736</v>
       </c>
       <c r="R18" t="n">
-        <v>7192696</v>
+        <v>7192698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113703224</v>
+        <v>113703220</v>
       </c>
       <c r="B19" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750724</v>
+        <v>750786</v>
       </c>
       <c r="R19" t="n">
-        <v>7193030</v>
+        <v>7192980</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113703221</v>
+        <v>113703213</v>
       </c>
       <c r="B20" t="n">
-        <v>90153</v>
+        <v>90099</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,25 +2611,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750789</v>
+        <v>750660</v>
       </c>
       <c r="R20" t="n">
-        <v>7193000</v>
+        <v>7193051</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113703223</v>
+        <v>113703191</v>
       </c>
       <c r="B21" t="n">
-        <v>90153</v>
+        <v>79298</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,25 +2718,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750773</v>
+        <v>750735</v>
       </c>
       <c r="R21" t="n">
-        <v>7193000</v>
+        <v>7192695</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113703219</v>
+        <v>113703193</v>
       </c>
       <c r="B22" t="n">
-        <v>90135</v>
+        <v>78236</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750793</v>
+        <v>750514</v>
       </c>
       <c r="R22" t="n">
-        <v>7192970</v>
+        <v>7192817</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113703211</v>
+        <v>113703198</v>
       </c>
       <c r="B23" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750676</v>
+        <v>750498</v>
       </c>
       <c r="R23" t="n">
-        <v>7192911</v>
+        <v>7192778</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113703202</v>
+        <v>113703200</v>
       </c>
       <c r="B24" t="n">
-        <v>78201</v>
+        <v>79265</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750725</v>
+        <v>750567</v>
       </c>
       <c r="R24" t="n">
-        <v>7192721</v>
+        <v>7192769</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113703217</v>
+        <v>113703211</v>
       </c>
       <c r="B25" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750701</v>
+        <v>750676</v>
       </c>
       <c r="R25" t="n">
-        <v>7193021</v>
+        <v>7192911</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113703168</v>
+        <v>113703219</v>
       </c>
       <c r="B26" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750652</v>
+        <v>750793</v>
       </c>
       <c r="R26" t="n">
-        <v>7192891</v>
+        <v>7192970</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113703198</v>
+        <v>113703199</v>
       </c>
       <c r="B27" t="n">
-        <v>90135</v>
+        <v>79299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,25 +3360,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750498</v>
+        <v>750567</v>
       </c>
       <c r="R27" t="n">
-        <v>7192778</v>
+        <v>7192769</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113703210</v>
+        <v>113703224</v>
       </c>
       <c r="B28" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>750636</v>
+        <v>750724</v>
       </c>
       <c r="R28" t="n">
-        <v>7192848</v>
+        <v>7193030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113703222</v>
+        <v>113703192</v>
       </c>
       <c r="B29" t="n">
-        <v>90153</v>
+        <v>79265</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750782</v>
+        <v>750737</v>
       </c>
       <c r="R29" t="n">
-        <v>7192990</v>
+        <v>7192696</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113703194</v>
+        <v>113703223</v>
       </c>
       <c r="B30" t="n">
-        <v>78201</v>
+        <v>90153</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750520</v>
+        <v>750773</v>
       </c>
       <c r="R30" t="n">
-        <v>7192806</v>
+        <v>7193000</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113703190</v>
+        <v>113703188</v>
       </c>
       <c r="B31" t="n">
-        <v>79299</v>
+        <v>78201</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,25 +3788,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>750736</v>
+        <v>750810</v>
       </c>
       <c r="R31" t="n">
-        <v>7192698</v>
+        <v>7192675</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113703201</v>
+        <v>113703168</v>
       </c>
       <c r="B32" t="n">
         <v>81944</v>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750591</v>
+        <v>750652</v>
       </c>
       <c r="R32" t="n">
-        <v>7192765</v>
+        <v>7192891</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113703216</v>
+        <v>113703201</v>
       </c>
       <c r="B33" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>750665</v>
+        <v>750591</v>
       </c>
       <c r="R33" t="n">
-        <v>7193040</v>
+        <v>7192765</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703195</v>
+        <v>113703169</v>
       </c>
       <c r="B4" t="n">
-        <v>97422</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750470</v>
+        <v>750724</v>
       </c>
       <c r="R4" t="n">
-        <v>7192856</v>
+        <v>7193030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703197</v>
+        <v>113703223</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>90153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750492</v>
+        <v>750773</v>
       </c>
       <c r="R5" t="n">
-        <v>7192773</v>
+        <v>7193000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703216</v>
+        <v>113703192</v>
       </c>
       <c r="B6" t="n">
-        <v>90135</v>
+        <v>79265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750665</v>
+        <v>750737</v>
       </c>
       <c r="R6" t="n">
-        <v>7193040</v>
+        <v>7192696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703194</v>
+        <v>113703199</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>79299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750520</v>
+        <v>750567</v>
       </c>
       <c r="R7" t="n">
-        <v>7192806</v>
+        <v>7192769</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113703202</v>
+        <v>113703190</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>79299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750725</v>
+        <v>750736</v>
       </c>
       <c r="R8" t="n">
-        <v>7192721</v>
+        <v>7192698</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113703212</v>
+        <v>113703210</v>
       </c>
       <c r="B9" t="n">
         <v>90153</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750715</v>
+        <v>750636</v>
       </c>
       <c r="R9" t="n">
-        <v>7193010</v>
+        <v>7192848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113703215</v>
+        <v>113703191</v>
       </c>
       <c r="B10" t="n">
-        <v>90153</v>
+        <v>79298</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750649</v>
+        <v>750735</v>
       </c>
       <c r="R10" t="n">
-        <v>7193005</v>
+        <v>7192695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113703196</v>
+        <v>113703168</v>
       </c>
       <c r="B11" t="n">
-        <v>90099</v>
+        <v>81944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750481</v>
+        <v>750652</v>
       </c>
       <c r="R11" t="n">
-        <v>7192771</v>
+        <v>7192891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113703204</v>
+        <v>113703219</v>
       </c>
       <c r="B12" t="n">
-        <v>97422</v>
+        <v>90135</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750792</v>
+        <v>750793</v>
       </c>
       <c r="R12" t="n">
-        <v>7192947</v>
+        <v>7192970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113703221</v>
+        <v>113703188</v>
       </c>
       <c r="B13" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750789</v>
+        <v>750810</v>
       </c>
       <c r="R13" t="n">
-        <v>7193000</v>
+        <v>7192675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1957,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113703210</v>
+        <v>113703222</v>
       </c>
       <c r="B14" t="n">
         <v>90153</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750636</v>
+        <v>750782</v>
       </c>
       <c r="R14" t="n">
-        <v>7192848</v>
+        <v>7192990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113703217</v>
+        <v>113703221</v>
       </c>
       <c r="B15" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750701</v>
+        <v>750789</v>
       </c>
       <c r="R15" t="n">
-        <v>7193021</v>
+        <v>7193000</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113703218</v>
+        <v>113703217</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750692</v>
+        <v>750701</v>
       </c>
       <c r="R16" t="n">
-        <v>7192995</v>
+        <v>7193021</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113703222</v>
+        <v>113703216</v>
       </c>
       <c r="B17" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750782</v>
+        <v>750665</v>
       </c>
       <c r="R17" t="n">
-        <v>7192990</v>
+        <v>7193040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113703190</v>
+        <v>113703198</v>
       </c>
       <c r="B18" t="n">
-        <v>79299</v>
+        <v>90135</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750736</v>
+        <v>750498</v>
       </c>
       <c r="R18" t="n">
-        <v>7192698</v>
+        <v>7192778</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113703220</v>
+        <v>113703211</v>
       </c>
       <c r="B19" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750786</v>
+        <v>750676</v>
       </c>
       <c r="R19" t="n">
-        <v>7192980</v>
+        <v>7192911</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113703213</v>
+        <v>113703196</v>
       </c>
       <c r="B20" t="n">
         <v>90099</v>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750660</v>
+        <v>750481</v>
       </c>
       <c r="R20" t="n">
-        <v>7193051</v>
+        <v>7192771</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113703191</v>
+        <v>113703195</v>
       </c>
       <c r="B21" t="n">
-        <v>79298</v>
+        <v>97422</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750735</v>
+        <v>750470</v>
       </c>
       <c r="R21" t="n">
-        <v>7192695</v>
+        <v>7192856</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113703193</v>
+        <v>113703204</v>
       </c>
       <c r="B22" t="n">
-        <v>78236</v>
+        <v>97422</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,25 +2825,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750514</v>
+        <v>750792</v>
       </c>
       <c r="R22" t="n">
-        <v>7192817</v>
+        <v>7192947</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113703198</v>
+        <v>113703197</v>
       </c>
       <c r="B23" t="n">
-        <v>90135</v>
+        <v>79199</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2932,25 +2932,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750498</v>
+        <v>750492</v>
       </c>
       <c r="R23" t="n">
-        <v>7192778</v>
+        <v>7192773</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113703200</v>
+        <v>113703220</v>
       </c>
       <c r="B24" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750567</v>
+        <v>750786</v>
       </c>
       <c r="R24" t="n">
-        <v>7192769</v>
+        <v>7192980</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113703211</v>
+        <v>113703193</v>
       </c>
       <c r="B25" t="n">
-        <v>78201</v>
+        <v>78236</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750676</v>
+        <v>750514</v>
       </c>
       <c r="R25" t="n">
-        <v>7192911</v>
+        <v>7192817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113703219</v>
+        <v>113703218</v>
       </c>
       <c r="B26" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750793</v>
+        <v>750692</v>
       </c>
       <c r="R26" t="n">
-        <v>7192970</v>
+        <v>7192995</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113703199</v>
+        <v>113703194</v>
       </c>
       <c r="B27" t="n">
-        <v>79299</v>
+        <v>78201</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,25 +3360,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750567</v>
+        <v>750520</v>
       </c>
       <c r="R27" t="n">
-        <v>7192769</v>
+        <v>7192806</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113703224</v>
+        <v>113703212</v>
       </c>
       <c r="B28" t="n">
-        <v>78201</v>
+        <v>90153</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>750724</v>
+        <v>750715</v>
       </c>
       <c r="R28" t="n">
-        <v>7193030</v>
+        <v>7193010</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113703192</v>
+        <v>113703202</v>
       </c>
       <c r="B29" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750737</v>
+        <v>750725</v>
       </c>
       <c r="R29" t="n">
-        <v>7192696</v>
+        <v>7192721</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113703223</v>
+        <v>113703213</v>
       </c>
       <c r="B30" t="n">
-        <v>90153</v>
+        <v>90099</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750773</v>
+        <v>750660</v>
       </c>
       <c r="R30" t="n">
-        <v>7193000</v>
+        <v>7193051</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113703188</v>
+        <v>113703215</v>
       </c>
       <c r="B31" t="n">
-        <v>78201</v>
+        <v>90153</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3792,21 +3792,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>750810</v>
+        <v>750649</v>
       </c>
       <c r="R31" t="n">
-        <v>7192675</v>
+        <v>7193005</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113703168</v>
+        <v>113703200</v>
       </c>
       <c r="B32" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3899,21 +3899,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750652</v>
+        <v>750567</v>
       </c>
       <c r="R32" t="n">
-        <v>7192891</v>
+        <v>7192769</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113703191</v>
+        <v>113703219</v>
       </c>
       <c r="B10" t="n">
-        <v>79298</v>
+        <v>90135</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750735</v>
+        <v>750793</v>
       </c>
       <c r="R10" t="n">
-        <v>7192695</v>
+        <v>7192970</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113703168</v>
+        <v>113703188</v>
       </c>
       <c r="B11" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750652</v>
+        <v>750810</v>
       </c>
       <c r="R11" t="n">
-        <v>7192891</v>
+        <v>7192675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113703219</v>
+        <v>113703191</v>
       </c>
       <c r="B12" t="n">
-        <v>90135</v>
+        <v>79298</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750793</v>
+        <v>750735</v>
       </c>
       <c r="R12" t="n">
-        <v>7192970</v>
+        <v>7192695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113703188</v>
+        <v>113703168</v>
       </c>
       <c r="B13" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750810</v>
+        <v>750652</v>
       </c>
       <c r="R13" t="n">
-        <v>7192675</v>
+        <v>7192891</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113703221</v>
+        <v>113703217</v>
       </c>
       <c r="B15" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750789</v>
+        <v>750701</v>
       </c>
       <c r="R15" t="n">
-        <v>7193000</v>
+        <v>7193021</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113703217</v>
+        <v>113703221</v>
       </c>
       <c r="B16" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750701</v>
+        <v>750789</v>
       </c>
       <c r="R16" t="n">
-        <v>7193021</v>
+        <v>7193000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113703196</v>
+        <v>113703195</v>
       </c>
       <c r="B20" t="n">
-        <v>90099</v>
+        <v>97422</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750481</v>
+        <v>750470</v>
       </c>
       <c r="R20" t="n">
-        <v>7192771</v>
+        <v>7192856</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113703195</v>
+        <v>113703196</v>
       </c>
       <c r="B21" t="n">
-        <v>97422</v>
+        <v>90099</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750470</v>
+        <v>750481</v>
       </c>
       <c r="R21" t="n">
-        <v>7192856</v>
+        <v>7192771</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113703204</v>
+        <v>113703197</v>
       </c>
       <c r="B22" t="n">
-        <v>97422</v>
+        <v>79199</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750792</v>
+        <v>750492</v>
       </c>
       <c r="R22" t="n">
-        <v>7192947</v>
+        <v>7192773</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113703197</v>
+        <v>113703220</v>
       </c>
       <c r="B23" t="n">
-        <v>79199</v>
+        <v>81944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2932,25 +2932,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750492</v>
+        <v>750786</v>
       </c>
       <c r="R23" t="n">
-        <v>7192773</v>
+        <v>7192980</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113703220</v>
+        <v>113703204</v>
       </c>
       <c r="B24" t="n">
-        <v>81944</v>
+        <v>97422</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750786</v>
+        <v>750792</v>
       </c>
       <c r="R24" t="n">
-        <v>7192980</v>
+        <v>7192947</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703169</v>
+        <v>113703210</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>90153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750724</v>
+        <v>750636</v>
       </c>
       <c r="R4" t="n">
-        <v>7193030</v>
+        <v>7192848</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703223</v>
+        <v>113703217</v>
       </c>
       <c r="B5" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750773</v>
+        <v>750701</v>
       </c>
       <c r="R5" t="n">
-        <v>7193000</v>
+        <v>7193021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703192</v>
+        <v>113703212</v>
       </c>
       <c r="B6" t="n">
-        <v>79265</v>
+        <v>90153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750737</v>
+        <v>750715</v>
       </c>
       <c r="R6" t="n">
-        <v>7192696</v>
+        <v>7193010</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703199</v>
+        <v>113703216</v>
       </c>
       <c r="B7" t="n">
-        <v>79299</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750567</v>
+        <v>750665</v>
       </c>
       <c r="R7" t="n">
-        <v>7192769</v>
+        <v>7193040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113703190</v>
+        <v>113703211</v>
       </c>
       <c r="B8" t="n">
-        <v>79299</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750736</v>
+        <v>750676</v>
       </c>
       <c r="R8" t="n">
-        <v>7192698</v>
+        <v>7192911</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113703210</v>
+        <v>113703169</v>
       </c>
       <c r="B9" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750636</v>
+        <v>750724</v>
       </c>
       <c r="R9" t="n">
-        <v>7192848</v>
+        <v>7193030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113703219</v>
+        <v>113703202</v>
       </c>
       <c r="B10" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750793</v>
+        <v>750725</v>
       </c>
       <c r="R10" t="n">
-        <v>7192970</v>
+        <v>7192721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113703188</v>
+        <v>113703197</v>
       </c>
       <c r="B11" t="n">
-        <v>78201</v>
+        <v>79199</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750810</v>
+        <v>750492</v>
       </c>
       <c r="R11" t="n">
-        <v>7192675</v>
+        <v>7192773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113703191</v>
+        <v>113703190</v>
       </c>
       <c r="B12" t="n">
-        <v>79298</v>
+        <v>79299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750735</v>
+        <v>750736</v>
       </c>
       <c r="R12" t="n">
-        <v>7192695</v>
+        <v>7192698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113703168</v>
+        <v>113703198</v>
       </c>
       <c r="B13" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750652</v>
+        <v>750498</v>
       </c>
       <c r="R13" t="n">
-        <v>7192891</v>
+        <v>7192778</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113703222</v>
+        <v>113703213</v>
       </c>
       <c r="B14" t="n">
-        <v>90153</v>
+        <v>90099</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750782</v>
+        <v>750660</v>
       </c>
       <c r="R14" t="n">
-        <v>7192990</v>
+        <v>7193051</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113703217</v>
+        <v>113703221</v>
       </c>
       <c r="B15" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750701</v>
+        <v>750789</v>
       </c>
       <c r="R15" t="n">
-        <v>7193021</v>
+        <v>7193000</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113703221</v>
+        <v>113703219</v>
       </c>
       <c r="B16" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750789</v>
+        <v>750793</v>
       </c>
       <c r="R16" t="n">
-        <v>7193000</v>
+        <v>7192970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113703216</v>
+        <v>113703220</v>
       </c>
       <c r="B17" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750665</v>
+        <v>750786</v>
       </c>
       <c r="R17" t="n">
-        <v>7193040</v>
+        <v>7192980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113703198</v>
+        <v>113703196</v>
       </c>
       <c r="B18" t="n">
-        <v>90135</v>
+        <v>90099</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750498</v>
+        <v>750481</v>
       </c>
       <c r="R18" t="n">
-        <v>7192778</v>
+        <v>7192771</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113703211</v>
+        <v>113703188</v>
       </c>
       <c r="B19" t="n">
         <v>78201</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750676</v>
+        <v>750810</v>
       </c>
       <c r="R19" t="n">
-        <v>7192911</v>
+        <v>7192675</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113703195</v>
+        <v>113703200</v>
       </c>
       <c r="B20" t="n">
-        <v>97422</v>
+        <v>79265</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,25 +2611,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750470</v>
+        <v>750567</v>
       </c>
       <c r="R20" t="n">
-        <v>7192856</v>
+        <v>7192769</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113703196</v>
+        <v>113703194</v>
       </c>
       <c r="B21" t="n">
-        <v>90099</v>
+        <v>78201</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,25 +2718,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750481</v>
+        <v>750520</v>
       </c>
       <c r="R21" t="n">
-        <v>7192771</v>
+        <v>7192806</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113703197</v>
+        <v>113703192</v>
       </c>
       <c r="B22" t="n">
-        <v>79199</v>
+        <v>79265</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,25 +2825,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750492</v>
+        <v>750737</v>
       </c>
       <c r="R22" t="n">
-        <v>7192773</v>
+        <v>7192696</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113703220</v>
+        <v>113703168</v>
       </c>
       <c r="B23" t="n">
         <v>81944</v>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750786</v>
+        <v>750652</v>
       </c>
       <c r="R23" t="n">
-        <v>7192980</v>
+        <v>7192891</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113703204</v>
+        <v>113703201</v>
       </c>
       <c r="B24" t="n">
-        <v>97422</v>
+        <v>81944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750792</v>
+        <v>750591</v>
       </c>
       <c r="R24" t="n">
-        <v>7192947</v>
+        <v>7192765</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113703193</v>
+        <v>113703223</v>
       </c>
       <c r="B25" t="n">
-        <v>78236</v>
+        <v>90153</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750514</v>
+        <v>750773</v>
       </c>
       <c r="R25" t="n">
-        <v>7192817</v>
+        <v>7193000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113703218</v>
+        <v>113703193</v>
       </c>
       <c r="B26" t="n">
-        <v>78201</v>
+        <v>78236</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750692</v>
+        <v>750514</v>
       </c>
       <c r="R26" t="n">
-        <v>7192995</v>
+        <v>7192817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113703194</v>
+        <v>113703191</v>
       </c>
       <c r="B27" t="n">
-        <v>78201</v>
+        <v>79298</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,20 +3360,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750520</v>
+        <v>750735</v>
       </c>
       <c r="R27" t="n">
-        <v>7192806</v>
+        <v>7192695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113703212</v>
+        <v>113703199</v>
       </c>
       <c r="B28" t="n">
-        <v>90153</v>
+        <v>79299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,25 +3467,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>750715</v>
+        <v>750567</v>
       </c>
       <c r="R28" t="n">
-        <v>7193010</v>
+        <v>7192769</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113703202</v>
+        <v>113703218</v>
       </c>
       <c r="B29" t="n">
         <v>78201</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750725</v>
+        <v>750692</v>
       </c>
       <c r="R29" t="n">
-        <v>7192721</v>
+        <v>7192995</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113703213</v>
+        <v>113703204</v>
       </c>
       <c r="B30" t="n">
-        <v>90099</v>
+        <v>97422</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750660</v>
+        <v>750792</v>
       </c>
       <c r="R30" t="n">
-        <v>7193051</v>
+        <v>7192947</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113703215</v>
+        <v>113703195</v>
       </c>
       <c r="B31" t="n">
-        <v>90153</v>
+        <v>97422</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,25 +3788,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>750649</v>
+        <v>750470</v>
       </c>
       <c r="R31" t="n">
-        <v>7193005</v>
+        <v>7192856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113703200</v>
+        <v>113703222</v>
       </c>
       <c r="B32" t="n">
-        <v>79265</v>
+        <v>90153</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3899,21 +3899,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750567</v>
+        <v>750782</v>
       </c>
       <c r="R32" t="n">
-        <v>7192769</v>
+        <v>7192990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113703201</v>
+        <v>113703215</v>
       </c>
       <c r="B33" t="n">
-        <v>81944</v>
+        <v>90153</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>750591</v>
+        <v>750649</v>
       </c>
       <c r="R33" t="n">
-        <v>7192765</v>
+        <v>7193005</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31079-2021 artfynd.xlsx
+++ b/artfynd/A 31079-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
